--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -3308,7 +3308,7 @@
         <v>136106654</v>
       </c>
       <c r="B26" t="n">
-        <v>97997</v>
+        <v>98000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>136106530</v>
       </c>
       <c r="B53" t="n">
-        <v>91872</v>
+        <v>91881</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>136104030</v>
       </c>
       <c r="B109" t="n">
-        <v>99320</v>
+        <v>99323</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>136106670</v>
       </c>
       <c r="B110" t="n">
-        <v>98363</v>
+        <v>98366</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>136106545</v>
       </c>
       <c r="B111" t="n">
-        <v>108437</v>
+        <v>108440</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>136106660</v>
       </c>
       <c r="B112" t="n">
-        <v>108437</v>
+        <v>108440</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>136106552</v>
       </c>
       <c r="B115" t="n">
-        <v>106358</v>
+        <v>106361</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>136106673</v>
       </c>
       <c r="B116" t="n">
-        <v>106358</v>
+        <v>106361</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>136104024</v>
       </c>
       <c r="B129" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>136104040</v>
       </c>
       <c r="B130" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>136106695</v>
       </c>
       <c r="B131" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>136104037</v>
       </c>
       <c r="B133" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>136106667</v>
       </c>
       <c r="B134" t="n">
-        <v>101473</v>
+        <v>101476</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>136609492</v>
       </c>
       <c r="B142" t="n">
-        <v>91607</v>
+        <v>91609</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>136104021</v>
       </c>
       <c r="B147" t="n">
-        <v>93403</v>
+        <v>93406</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>136609516</v>
       </c>
       <c r="B149" t="n">
-        <v>93428</v>
+        <v>93431</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -3308,7 +3308,7 @@
         <v>136106654</v>
       </c>
       <c r="B26" t="n">
-        <v>98000</v>
+        <v>98001</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>136106530</v>
       </c>
       <c r="B53" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>136104030</v>
       </c>
       <c r="B109" t="n">
-        <v>99323</v>
+        <v>99324</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>136106670</v>
       </c>
       <c r="B110" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>136106545</v>
       </c>
       <c r="B111" t="n">
-        <v>108440</v>
+        <v>108441</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>136106660</v>
       </c>
       <c r="B112" t="n">
-        <v>108440</v>
+        <v>108441</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>136106552</v>
       </c>
       <c r="B115" t="n">
-        <v>106361</v>
+        <v>106362</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>136106673</v>
       </c>
       <c r="B116" t="n">
-        <v>106361</v>
+        <v>106362</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>136104024</v>
       </c>
       <c r="B129" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>136104040</v>
       </c>
       <c r="B130" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>136106695</v>
       </c>
       <c r="B131" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>136104037</v>
       </c>
       <c r="B133" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>136106667</v>
       </c>
       <c r="B134" t="n">
-        <v>101476</v>
+        <v>101477</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>136104021</v>
       </c>
       <c r="B147" t="n">
-        <v>93406</v>
+        <v>93407</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>136609516</v>
       </c>
       <c r="B149" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -3308,7 +3308,7 @@
         <v>136106654</v>
       </c>
       <c r="B26" t="n">
-        <v>98001</v>
+        <v>98006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>136106530</v>
       </c>
       <c r="B53" t="n">
-        <v>91882</v>
+        <v>91887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>136106833</v>
       </c>
       <c r="B100" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>136104030</v>
       </c>
       <c r="B109" t="n">
-        <v>99324</v>
+        <v>99329</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>136106670</v>
       </c>
       <c r="B110" t="n">
-        <v>98367</v>
+        <v>98372</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>136106545</v>
       </c>
       <c r="B111" t="n">
-        <v>108441</v>
+        <v>108446</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>136106660</v>
       </c>
       <c r="B112" t="n">
-        <v>108441</v>
+        <v>108446</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>136106552</v>
       </c>
       <c r="B115" t="n">
-        <v>106362</v>
+        <v>106367</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>136106673</v>
       </c>
       <c r="B116" t="n">
-        <v>106362</v>
+        <v>106367</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>136104024</v>
       </c>
       <c r="B129" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>136104040</v>
       </c>
       <c r="B130" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>136106695</v>
       </c>
       <c r="B131" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>136104037</v>
       </c>
       <c r="B133" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>136106667</v>
       </c>
       <c r="B134" t="n">
-        <v>101477</v>
+        <v>101482</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>136609492</v>
       </c>
       <c r="B142" t="n">
-        <v>91609</v>
+        <v>91611</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>136104021</v>
       </c>
       <c r="B147" t="n">
-        <v>93407</v>
+        <v>93412</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>136609516</v>
       </c>
       <c r="B149" t="n">
-        <v>93432</v>
+        <v>93437</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -16388,7 +16388,7 @@
         <v>136609492</v>
       </c>
       <c r="B142" t="n">
-        <v>91611</v>
+        <v>91613</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>136609516</v>
       </c>
       <c r="B149" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -16388,7 +16388,7 @@
         <v>136609492</v>
       </c>
       <c r="B142" t="n">
-        <v>91613</v>
+        <v>91615</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>136609516</v>
       </c>
       <c r="B149" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -16388,7 +16388,7 @@
         <v>136609492</v>
       </c>
       <c r="B142" t="n">
-        <v>91615</v>
+        <v>91617</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>136609516</v>
       </c>
       <c r="B149" t="n">
-        <v>93441</v>
+        <v>93443</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -16388,7 +16388,7 @@
         <v>136609492</v>
       </c>
       <c r="B142" t="n">
-        <v>91617</v>
+        <v>91618</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>136609516</v>
       </c>
       <c r="B149" t="n">
-        <v>93443</v>
+        <v>93444</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -16388,7 +16388,7 @@
         <v>136609492</v>
       </c>
       <c r="B142" t="n">
-        <v>91618</v>
+        <v>91624</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>136609516</v>
       </c>
       <c r="B149" t="n">
-        <v>93444</v>
+        <v>93450</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -16388,7 +16388,7 @@
         <v>136609492</v>
       </c>
       <c r="B142" t="n">
-        <v>91624</v>
+        <v>91628</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>136609516</v>
       </c>
       <c r="B149" t="n">
-        <v>93450</v>
+        <v>93454</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -16388,7 +16388,7 @@
         <v>136609492</v>
       </c>
       <c r="B142" t="n">
-        <v>91628</v>
+        <v>91630</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>136609516</v>
       </c>
       <c r="B149" t="n">
-        <v>93454</v>
+        <v>93456</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -16388,7 +16388,7 @@
         <v>136609492</v>
       </c>
       <c r="B142" t="n">
-        <v>91630</v>
+        <v>91643</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>136609516</v>
       </c>
       <c r="B149" t="n">
-        <v>93456</v>
+        <v>93469</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -3646,7 +3646,7 @@
         <v>137308932</v>
       </c>
       <c r="B29" t="n">
-        <v>90892</v>
+        <v>90893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -3646,7 +3646,7 @@
         <v>137308932</v>
       </c>
       <c r="B29" t="n">
-        <v>90893</v>
+        <v>90896</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -3646,7 +3646,7 @@
         <v>137308932</v>
       </c>
       <c r="B29" t="n">
-        <v>90896</v>
+        <v>90901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -3646,7 +3646,7 @@
         <v>137308932</v>
       </c>
       <c r="B29" t="n">
-        <v>90901</v>
+        <v>90912</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -3646,7 +3646,7 @@
         <v>137308932</v>
       </c>
       <c r="B29" t="n">
-        <v>90912</v>
+        <v>90913</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -3646,7 +3646,7 @@
         <v>137308932</v>
       </c>
       <c r="B29" t="n">
-        <v>90913</v>
+        <v>90916</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -3646,7 +3646,7 @@
         <v>137308932</v>
       </c>
       <c r="B29" t="n">
-        <v>90916</v>
+        <v>90920</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
